--- a/data/trans_orig/P6703-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6703-Edad-trans_orig.xlsx
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36639</t>
+          <t>36974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59742</t>
+          <t>60564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54785</t>
+          <t>55047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79796</t>
+          <t>77365</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>105230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>31814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>59059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68737</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108858</t>
+          <t>108904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>147880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129657</t>
+          <t>126893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65314</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96442</t>
+          <t>97036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164367</t>
+          <t>164000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210923</t>
+          <t>211951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167573</t>
+          <t>167668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208265</t>
+          <t>205180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105635</t>
+          <t>105901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>140262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>284532</t>
+          <t>286080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336129</t>
+          <t>338796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21816</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>39745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67534</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>100843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41413</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67896</t>
+          <t>67276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>115326</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157981</t>
+          <t>158109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113870</t>
+          <t>112953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152315</t>
+          <t>150765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67971</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>98589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190363</t>
+          <t>189048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240033</t>
+          <t>238633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170933</t>
+          <t>170274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211258</t>
+          <t>212606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115182</t>
+          <t>114583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>147489</t>
+          <t>149640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294719</t>
+          <t>296085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348077</t>
+          <t>350406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25301</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56284</t>
+          <t>57719</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89271</t>
+          <t>90225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>53706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93428</t>
+          <t>93332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134879</t>
+          <t>135263</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101272</t>
+          <t>103177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>139801</t>
+          <t>142587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>53494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>84292</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166718</t>
+          <t>167208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>213499</t>
+          <t>217527</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>138884</t>
+          <t>138655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179621</t>
+          <t>177570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82123</t>
+          <t>82765</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113650</t>
+          <t>114959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>231191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282485</t>
+          <t>280685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>32950</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58043</t>
+          <t>59734</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34454</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51236</t>
+          <t>51894</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>78730</t>
+          <t>80284</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>65544</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90719</t>
+          <t>90591</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41853</t>
+          <t>41286</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94109</t>
+          <t>94506</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>124810</t>
+          <t>125844</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>75410</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>46078</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>52717</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>84535</t>
+          <t>87411</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>239966</t>
+          <t>239989</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>299027</t>
+          <t>301776</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>147794</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>198636</t>
+          <t>200046</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>406423</t>
+          <t>404977</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>482096</t>
+          <t>484093</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>393242</t>
+          <t>396048</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>467545</t>
+          <t>466308</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>248692</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>306944</t>
+          <t>309988</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>664296</t>
+          <t>660794</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>757598</t>
+          <t>755024</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>617714</t>
+          <t>621850</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>697278</t>
+          <t>699229</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>397847</t>
+          <t>400927</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>466188</t>
+          <t>463240</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1043574</t>
+          <t>1043749</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1144173</t>
+          <t>1142433</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>23812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>25385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22057</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39606</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42236</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67673</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>24734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43830</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56106</t>
+          <t>56083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81498</t>
+          <t>81965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29637</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28989</t>
+          <t>29288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>32469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>31309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54872</t>
+          <t>55882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>54165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83013</t>
+          <t>84713</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>87414</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124685</t>
+          <t>123745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96322</t>
+          <t>96580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132149</t>
+          <t>130217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>67385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95629</t>
+          <t>96815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170996</t>
+          <t>171167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216128</t>
+          <t>217902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116457</t>
+          <t>114443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151360</t>
+          <t>151732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109122</t>
+          <t>110841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141844</t>
+          <t>141268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235231</t>
+          <t>234862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>283398</t>
+          <t>283519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39732</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60114</t>
+          <t>57524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67031</t>
+          <t>66221</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102682</t>
+          <t>100683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47276</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74760</t>
+          <t>75757</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121759</t>
+          <t>120973</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>163731</t>
+          <t>164572</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141843</t>
+          <t>143827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186227</t>
+          <t>184032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>73904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>105525</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225739</t>
+          <t>227648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>279946</t>
+          <t>279342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151270</t>
+          <t>149538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193498</t>
+          <t>192797</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125364</t>
+          <t>124976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159792</t>
+          <t>158290</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>288606</t>
+          <t>286935</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345406</t>
+          <t>342283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29084</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22885</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21443</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43425</t>
+          <t>43207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77130</t>
+          <t>77394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26092</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49089</t>
+          <t>50447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82585</t>
+          <t>80719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118537</t>
+          <t>120056</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105984</t>
+          <t>105554</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146197</t>
+          <t>143585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>88830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175312</t>
+          <t>173257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222675</t>
+          <t>220982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134144</t>
+          <t>135550</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>174910</t>
+          <t>175337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>95034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>128661</t>
+          <t>127443</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240679</t>
+          <t>239210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291228</t>
+          <t>290330</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52033</t>
+          <t>52382</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49409</t>
+          <t>48243</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80085</t>
+          <t>78905</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26102</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49219</t>
+          <t>48352</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>29681</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>49458</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>61710</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>91051</t>
+          <t>93185</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62780</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90282</t>
+          <t>89732</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48036</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>98384</t>
+          <t>97459</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>131913</t>
+          <t>132487</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>51660</t>
+          <t>51009</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>59932</t>
+          <t>61172</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>58898</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>92533</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>76891</t>
+          <t>78155</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>112570</t>
+          <t>114209</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>158886</t>
+          <t>161380</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>241635</t>
+          <t>242647</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>302758</t>
+          <t>303751</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>150133</t>
+          <t>148891</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>198083</t>
+          <t>197227</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>405708</t>
+          <t>405899</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>485182</t>
+          <t>481489</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>432259</t>
+          <t>428687</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>503993</t>
+          <t>503720</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>282652</t>
+          <t>278017</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>336945</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>730550</t>
+          <t>733737</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>823800</t>
+          <t>825318</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>531787</t>
+          <t>533444</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>607872</t>
+          <t>610094</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>422213</t>
+          <t>425093</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>486106</t>
+          <t>489558</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>978164</t>
+          <t>978782</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1082131</t>
+          <t>1078964</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -12119,12 +12119,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -12335,32 +12335,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -12380,12 +12380,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12405,32 +12405,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -12448,32 +12448,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12483,32 +12483,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12518,32 +12518,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32057</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -12561,32 +12561,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12596,32 +12596,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12631,32 +12631,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -12674,17 +12674,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12709,17 +12709,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25150</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12744,17 +12744,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>58271</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>58271</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>58271</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12791,32 +12791,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -12836,12 +12836,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12861,32 +12861,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -12904,32 +12904,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12939,32 +12939,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12974,32 +12974,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -13017,32 +13017,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13052,32 +13052,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13087,32 +13087,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>37243</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -13130,32 +13130,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13165,32 +13165,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>33450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13200,32 +13200,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51051</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37278</t>
+          <t>41277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67256</t>
+          <t>71908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -13243,32 +13243,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44264</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30726</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58914</t>
+          <t>63238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13278,32 +13278,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44496</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35155</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53195</t>
+          <t>60275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13313,32 +13313,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>88760</t>
+          <t>99393</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72011</t>
+          <t>81930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103922</t>
+          <t>118012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -13356,17 +13356,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>118541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>118541</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>118541</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13391,17 +13391,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82336</t>
+          <t>93579</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82336</t>
+          <t>93579</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82336</t>
+          <t>93579</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13426,17 +13426,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>189389</t>
+          <t>212120</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>189389</t>
+          <t>212120</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>189389</t>
+          <t>212120</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13473,32 +13473,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13508,67 +13508,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>11503</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>20151</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>8,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>10293</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>5297</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>17831</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -13586,32 +13586,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13621,32 +13621,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13656,32 +13656,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -13699,32 +13699,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>28933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13734,32 +13734,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>22692</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13769,32 +13769,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>54897</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -13812,32 +13812,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25405</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37033</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13847,32 +13847,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13882,32 +13882,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46635</t>
+          <t>52725</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58167</t>
+          <t>67019</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -13925,32 +13925,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>49202</t>
+          <t>59371</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>48311</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>72117</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13960,32 +13960,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54132</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13995,32 +13995,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>94813</t>
+          <t>108651</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82620</t>
+          <t>93945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108347</t>
+          <t>124823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -14038,17 +14038,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>103383</t>
+          <t>121042</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103383</t>
+          <t>121042</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103383</t>
+          <t>121042</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14073,17 +14073,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93067</t>
+          <t>104885</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93067</t>
+          <t>104885</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93067</t>
+          <t>104885</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14108,17 +14108,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>196449</t>
+          <t>225927</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>196449</t>
+          <t>225927</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196449</t>
+          <t>225927</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14155,32 +14155,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14190,32 +14190,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14225,32 +14225,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -14268,32 +14268,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36436</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14303,32 +14303,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14338,32 +14338,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>15689</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37331</t>
+          <t>25132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -14381,32 +14381,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24546</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79812</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14416,32 +14416,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14451,32 +14451,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>45174</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>100500</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -14494,102 +14494,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28488</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>29744</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>22921</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>38349</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>31,58%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>64880</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>51255</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>78490</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>25,09%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>27297</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>20692</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>34713</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>31,11%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>55785</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>15160</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>121809</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -14607,32 +14607,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>298293</t>
+          <t>60007</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152793</t>
+          <t>47215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>350325</t>
+          <t>71001</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14642,32 +14642,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>56247</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>47397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60067</t>
+          <t>64893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14677,32 +14677,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>350156</t>
+          <t>116254</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>206321</t>
+          <t>100988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>441544</t>
+          <t>130887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -14720,17 +14720,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367170</t>
+          <t>137172</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367170</t>
+          <t>137172</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367170</t>
+          <t>137172</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14755,17 +14755,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>111580</t>
+          <t>121420</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>111580</t>
+          <t>121420</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>111580</t>
+          <t>121420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14790,17 +14790,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>478750</t>
+          <t>258592</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>478750</t>
+          <t>258592</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>478750</t>
+          <t>258592</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14837,32 +14837,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14872,7 +14872,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -14882,12 +14882,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14907,32 +14907,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -14950,32 +14950,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14985,32 +14985,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15020,32 +15020,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -15063,32 +15063,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15098,32 +15098,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>14454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15133,32 +15133,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>34663</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -15176,32 +15176,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23529</t>
+          <t>24289</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15211,32 +15211,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15246,32 +15246,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -15289,32 +15289,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16789</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31301</t>
+          <t>33407</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15324,32 +15324,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15359,32 +15359,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>38320</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47142</t>
+          <t>50724</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -15402,17 +15402,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>64838</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>64838</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>64838</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15437,17 +15437,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>36800</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36800</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36800</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15472,17 +15472,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>101637</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>101637</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>101637</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -15529,12 +15529,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>865</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15589,32 +15589,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>417</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -15745,7 +15745,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>812</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -15755,12 +15755,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -15790,12 +15790,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15815,17 +15815,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>560</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -15868,12 +15868,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -15903,12 +15903,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15928,32 +15928,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>459</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -15971,32 +15971,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -16006,32 +16006,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -16041,32 +16041,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -16084,17 +16084,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -16119,17 +16119,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -16154,17 +16154,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16836,17 +16836,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16883,32 +16883,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>42734</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16918,32 +16918,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16953,32 +16953,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56049</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -16996,32 +16996,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50970</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -17031,32 +17031,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17066,32 +17066,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>62849</t>
+          <t>61477</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -17109,32 +17109,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>80369</t>
+          <t>91752</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>136917</t>
+          <t>112920</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17144,32 +17144,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>69983</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17179,32 +17179,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>142191</t>
+          <t>161735</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>68144</t>
+          <t>140107</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>195171</t>
+          <t>183832</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -17222,32 +17222,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>96630</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>184829</t>
+          <t>139186</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -17257,32 +17257,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>91815</t>
+          <t>102347</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>108230</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -17292,32 +17292,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>200863</t>
+          <t>220185</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>193254</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>272495</t>
+          <t>247758</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -17335,32 +17335,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>212876</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>277185</t>
+          <t>186323</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>569652</t>
+          <t>239509</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17370,32 +17370,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>170385</t>
+          <t>187785</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>153925</t>
+          <t>170313</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>186984</t>
+          <t>206127</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -17405,32 +17405,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>599714</t>
+          <t>400661</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>458514</t>
+          <t>369767</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>839473</t>
+          <t>430117</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -17448,17 +17448,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -17483,17 +17483,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -17518,17 +17518,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
